--- a/output.xlsx
+++ b/output.xlsx
@@ -29,15 +29,21 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0068aad4"/>
+        <bgColor rgb="0068aad4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +57,26 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,4547 +443,4641 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y69"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>BB Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Implementation Status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>BB Tags(s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Functional Clusters</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Known Implementation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>ID (unique name)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Governance Applicable S-BB(s)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Compose BB(s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>What is needed to Design and Implement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>What is needed to build and run</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Non-Functional Requirements</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Dependencies to other Clusters</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Vehicle API Relevant</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Author/Company</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Related Project(s)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Availability of Source Code</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Availability of API</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Potential obstacles</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Maturity Badges</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>State (+ date of last change)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>System Context</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>CycloneDDS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>implementation exists</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>'- BB-SC; BB-MU; BB-CSC; BB-CMU</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>'- Communication</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>'- MWLayer</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>'- https://github.com/eclipse-cyclonedds/cyclonedds</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Eclipse Cyclone DDS is a very performant and robust open-source implementation of the OMG DDS specification. Cyclone DDS is developed completely in the open as an Eclipse IoT project (see eclipse-cyclone-dds) with a growing list of adopters (if you're one of them, please add your logo). It is a tier-1 middleware for the Robot Operating System ROS 2.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>'- Cyclone DDS aims at full coverage of the specs and today already covers most of this. With references to the individual OMG specifications, the following is available:  *    [DCPS](https://www.omg.org/spec/DDS/1.4/PDF) the base specification       *        zero configuration discovery (if multicast works)      *        publish/subscribe messaging      *        configurable storage of data in subscribers      *        many QoS settings - liveliness monitoring, deadlines, historical data, ...      *        coverage includes the Minimum, Ownership and (partially) Content profiles *    [DDS Security](https://www.omg.org/spec/DDS-SECURITY/1.1/PDF) - providing authentication, access control and encryption -  *    [DDS C++ API](https://www.omg.org/spec/DDS-PSM-Cxx/1.0/PDF) *    [DDS XTypes](https://www.omg.org/spec/DDS-XTypes/1.3/PDF) - the structural type system (some [caveats](https://github.com/eclipse-cyclonedds/cyclonedds/blob/master/docs/dev/xtypes_relnotes.md) here)  *    [DDSI-RTPS](https://www.omg.org/spec/DDSI-RTPS/2.5/PDF) - the interoperable network protocol</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>'- OS/Runtime Envirnoment</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>In order to build Cyclone DDS you need a Linux, Mac or Windows 10 machine (or, with some caveats, a *BSD, QNX, OpenIndiana or a Solaris 2.6 one) with the following installed on your host:  *    C compiler (most commonly GCC on Linux, Visual Studio on Windows, Xcode on macOS); *    Optionally GIT version control system; *    CMake, version 3.16 or later; *    Optionally OpenSSL, we recommend a fully patched and supported version but 1.1.1 will still work; *    Optionally Eclipse Iceoryx version 2.0 for shared memory and zero-copy support; *    Optionally Bison parser generator. A cached source is checked into the repository.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>* Real Time * QOS</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>'- Anonymous</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>'- https://projects.eclipse.org/projects/iot.cyclonedds</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>'- YES/Eclipse Public License - v 2.0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>|                       | Documentation | Requirements | Coding Guidelines | Testing | Release Process | | --------- |:-------------:|:------------:|:-----------------:|:-------:|:---------------:| | Level     | [Gold](https://cyclonedds.io/docs/) | Notdefined       | Notdefined | Notdefined | [Gold](https://cyclonedds.io/docs/) |</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>'- Used in several projects (e.g ROS2). - Last update Github Jan. 2025 / continuously updated</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>'- regarding details see section - What is needed to build and r</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>embeddedRTPS - DDS for Ressource-constrained environments</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>implementation exists</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>'- BB-SC, BB-CSC, BB-MU, BB-CMU</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>'- Communication</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>'- MWLayer</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>'- Github repo: &lt;https://github.com/embedded-software-laboratory/embeddedRTPS&gt;</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>This repository contains source code for embeddedRTPS, a portable and open-source C++ implementation of the Real-Time Publish-Subscribe Protocol (RTPS) for embedded system. RTPS is based on the publish-subscribe mechanism and is at the core of the Data Distribution Service (DDS). DDS is used, among many other applications, in Robot Operating System 2 (ROS2) and is also part of the AUTOSAR Adaptive platform. embeddedRTPS allows to integrate Ethernet-capable microcontrollers into DDS-based systems as first-class participants. embeddedRTPS is portable, as it only consumes lightweightIP and FreeRTOS APIs, which are available for a large number of embedded systems. embeddedRTPS avoids dynamic memory allocation once endpoints are constructed possible. Please note that embeddedRTPS only implements rudimentary Quality-of-Service (QoS) policies and is far from a complete RTPS implementation.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>'- This light-weight DDS stack allows to integrate ressource constraint devices into SOA architectures. DDS is used as a middleware in AUTOSAR Adaptive and ROS 2.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>'- https://www.omg.org/spec/DDS/ (deviations from spec.) - https://www.omg.org/spec/DDSI-RTPS/ (implemented partially)  - https://www.omg.org/spec/DDS-SECURITY/ (not implemented in pub version)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>'- FreeRTOS or other OS/Runtime Envirnoment - lwIP (could be another NW Stack)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>The Repo include a reference implementation which is executable on different Targets /STM32, AURIX Tricore. Needed: - MW Layer to use it with ROS2 (RMW) or adaptive AUTOSAR (commonAPI support). - Support for Security concepts in the OSS implementation. (see Applicable S-BB(s))</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>See: Example with a getting started for STM32 (Linux/Mac) GCC (Ubuntu 18 and above), Tasking Compiler,   &lt;https://github.com/embedded-software-laboratory/embeddedRTPS-STM32&gt;</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>'- Real-Time - Security</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>“No”</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>'- Alexandru Kampmann RWTH</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>'- &lt;https://github.com/mROS-base/mros2&gt; - &lt;https://github.com/micro-ROS&gt;</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Yes / License MIT Commercial Closed Source Parts are available (security)</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Yes / License MIT</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>| 			| Documentation | Requirements | Coding Guidelines | Testing | Release Process | | --------- |:-------------:|:------------:|:-----------------:|:-------:|:---------------:| | Level		| Notdefined | Notdefined   | Notdefined   | Notdefined	 | Notdefined |</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>'- First public release available, used in [unicaragil](https://www.unicaragil.de/en/) - last update Github Jul 2024</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>'- regarding details see section - What is needed to build and ru</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Fast-DDS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>implementation exists</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>'- BB-SC; BB-MU; BB-CSC; BB-CMU</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>'- Communication</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>'- MWLayer</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>'- https://github.com/eProsima/Fast-DDS</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>eprosima Fast DDS is a C++ implementation of the DDS (Data Distribution Service) standard of the OMG (Object Management Group). eProsima Fast DDS implements the RTPS (Real Time Publish Subscribe) protocol, which provides publisher-subscriber communications over unreliable transports such as UDP, as defined and maintained by the Object Management Group (OMG) consortium. RTPS is also the wire interoperability protocol defined for the Data Distribution Service (DDS) standard. eProsima Fast DDS expose an API to access directly the RTPS protocol, giving the user full access to the protocol internals.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>'- OS/Runtime Envirnoment</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>See [supported Platforms](https://github.com/eProsima/Fast-DDS/blob/master/PLATFORM_SUPPORT.md#platform-support)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>* Real Time * QOS</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>[eprosima](https://eprosima.com/)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>'- The most complete DDS - Proven: Plenty of success cases. Looking for commercial support? Contact info@eprosima.com  - https://eprosima.com/</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>'- YES/Apache 2.0</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>[Fast DDS CLI manual](https://fast-dds.docs.eprosima.com/en/latest/fastddscli/cli/cli.html)</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>|                       | Documentation | Requirements | Coding Guidelines | Testing | Release Process | | --------- |:-------------:|:------------:|:-----------------:|:-------:|:---------------:| | Level     | [Gold](https://fast-dds.docs.eprosima.com/en/latest/) | Notdefined       | [Gold](https://github.com/eProsima/Fast-DDS/blob/master/CONTRIBUTING.md) | Notdefined | [Gold](https://github.com/eProsima/Fast-DDS/blob/master/RELEASE_SUPPORT.md) |</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>'- Used in several projects (e.g ROS2). - last update Github Jan. 2025 / continuously updated</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>'- regarding details see section - What is needed to build and run  - Ubuntu/Debian, MacOS, Windows, Android, QN</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>OpenDDS</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>implementation exists</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>'- BB-SC; BB-MU; BB-CSC; BB-CMU</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>'- Communication</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>'- MWLayer</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>'- https://github.com/OpenDDS/OpenDDS</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>OpenDDS is an open-source C++ implementation of the Object Management Group's specification "Data Distribution Service for Real-time Systems" (DDS), as well as some other related specifications. These standards define a set of interfaces and protocols for developing distributed applications based on the publish-subscribe and distributed cache models. Although OpenDDS is itself developed in C++, Java bindings are provided so that Java applications can use OpenDDS. OpenDDS also includes support for the DDS Security and XTypes specifications.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>This release of OpenDDS is based on the DDS Specification formal/2015-04-10 (version 1.4). It features the following transport protocols:  *    TCP/IP *    UDP/IP *    IP multicast *    RTPS over UDP/IP (unicast and multicast) *    Shared memory  RTPS (Interoperability) features are based on the [DDS-RTPS Specification formal/2019-04-03 (version 2.3)](https://www.omg.org/spec/DDSI-RTPS/2.3). See the OpenDDS Developer's Guide and the file [docs/design/RTPS](https://github.com/OpenDDS/OpenDDS/blob/master/docs/design/RTPS) for more details on RTPS.  See the Developer's Guide for information on OpenDDS compliance with the DDS specification. If you would like to contribute a feature or sponsor the developers to add a feature please see the Support section above for contact information.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>'- OS/Runtime Envirnoment</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>These are just the required dependencies. For a complete detailed list of dependencies, including optional ones, see https://opendds.readthedocs.io/en/latest-release/devguide/building/dependencies.html.</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Operating Systems  This release of OpenDDS has been tested under the following platforms:  Linux family:  *    Red Hat EL and CentOS 6.6, 6.8, 6.9 (x86_64) *    Red Hat EL and CentOS 7.2, 7.3, 7.4 (x86_64) *    Red Hat EL 8.0 (x86_64) *    Fedora 24 and 31 (x86_64) *    Debian 9.4 (i686) *    Ubuntu 22.04 LTS (x86_64) *    openSUSE 42.1 (x86_64) *    Yocto 3.4.4 (ARMv8)  Windows family:  *   Windows 7 (32-bit, 64-bit) *    Windows Server 2012 R2 (64-bit) *    Windows 10 (64-bit)  Embedded/Mobile/IoT:  *    LynxOS-178 (OpenDDS Safety Profile) *    VxWorks 6.9, 7, 21.03 (see below) *    [Linux on Raspberry Pi](https://opendds.readthedocs.io/en/latest-release/devguide/quickstart/pi.html) *    [Android 9.0 "Pie" (API Level 28) NDK r18b](https://opendds.readthedocs.io/en/latest-release/devguide/building/android.html)  We have built OpenDDS for VxWorks 6.9, 7, and 21.03 and have run basic system and performance tests (but not the entire regression test suite). Please see the [OpenDDS Support page](https://opendds.org/support.html) for more information on support for ACE, TAO, and OpenDDS on VxWorks. Download VxWorks RPM packages for ACE, TAO, and OpenDDS [here](https://objectcomputing.com/products/opendds/vxworks).  Compilers  This release of OpenDDS has been tested using the following compilers:  *    Microsoft Visual C++ 10 with SP1 (Visual Studio 2010) *    Microsoft Visual C++ 11 (Visual Studio 2012) - Update 4 *   Microsoft Visual C++ 12 (Visual Studio 2013) - Update 5 *    Microsoft Visual C++ 14 (Visual Studio 2015) - Update 3 *    Microsoft Visual C++ 14.1 (Visual Studio 2017) cl 19.16.27048 *    Microsoft Visual C++ 14.2 (Visual Studio 2019) cl 19.29.30146 *    gcc 4.4.7, 4.8.5 *    gcc 6.2.1, 6.3.0 *    gcc 7.2.0, 7.3.0, 7.5.0 *    gcc 8.2.0, 8.2.1 *    gcc 9.3.1 *    gcc 12.2.0 *    Ubuntu clang 14.0.6 *    Ubuntu clang 15.0.0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>* Real Time * QOS</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>'- Anonymous</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>'- OpenDDS is an open source C++ implementation of the Object Management Group (OMG) Data Distribution Service (DDS). OpenDDS also supports Java bindings through JNI.  - http://www.opendds.org/</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>'- YES/OpenDDS (Licensed Product) is protected by copyright, and is distributed under the following terms.</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>| 			| Documentation | Requirements | Coding Guidelines | Testing | Release Process | | --------- |:-------------:|:------------:|:-----------------:|:-------:|:---------------:| | Level		| [Gold](https://opendds.readthedocs.io/en/latest-release/)| Notdefined | [Gold](https://opendds.readthedocs.io/en/latest-release/devguide/index.html)	| Notdefined	| [Gold](https://opendds.readthedocs.io/en/latest-release/news.html) |</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>'- Used in several projects (see  - Last Update Github Jan. 25 / continuously updated</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>'- Regarding details see section - What is needed to build and run  - Ubuntu/Debian/Red Hat, openSUSE, Yocto, Windows, LynxOS, VxWorks, Andro</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>vSOME/IP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>implementation exists</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>'- BB-SC; BB-MU; BB-CSC; BB-CMU</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>'- Communication</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>'- MWLayer</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>'- [vSomeIP](https://github.com/COVESA/vsomeip)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>SOME/IP is an abbreviation for "Scalable service-Oriented middlewarE over IP". This middleware was designed for typical automotive use cases and for being compatible with AUTOSAR (at least on the wire-format level). A publicly accessible specification is available [at](http://some-ip.com/). In this wiki we do not want to deepen further into the reasons for another middleware specification, but want to give a rough overview about the basic structures of the SOME/IP specification and its open source implementation vsomeip without any claim of completeness. [source](https://github.com/COVESA/vsomeip/wiki/vsomeip-in-10-minutes)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Open source implementation of the SOME/IP protocol. SOME/IP is an automotive middleware solution that can be used for control messages. It was designed from beginning on to fit devices of different sizes and different operating systems perfectly. This includes small devices like cameras, AUTOSAR devices, and up to head units or telematics devices. It was also made sure that SOME/IP supports features of the Infotainment domain as well as that of other domains in the vehicle, allowing SOME/IP to be used for MOST replacement scenarios as well as more traditional CAN scenarios. [source](https://some-ip.com/)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>[Standards](https://some-ip.com/standards.shtml) - AUTOSAR Classic - AUTOSAR Foundation - AUTOSAR Adaptive Platform - ISO 17215:2-2014 - Genivi/COVESA vsomeip</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>'- [see COVESA Github repo](https://github.com/COVESA/vsomeip)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>'- Anonymous</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>'- HAL4SDV, Shift2SDV</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>Yes / vSomeIP - Mozilla Public License Version 2.0</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>|                       | Documentation | Requirements | Coding Guidelines | Testing | Release Process | | --------- |:-------------:|:------------:|:-----------------:|:-------:|:---------------:| | Level     | [Silver](https://github.com/COVESA/vsomeip/wiki) | [Gold](https://github.com/COVESA/vsomeip/tree/master/test)       | [Gold](https://github.com/COVESA/vsomeip/wiki/vsomeip-Contribution-Process) | Notdefined | [Gold](https://github.com/COVESA/vsomeip/wiki/vsomeip-Release-Process) |</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>'- Used in several projects, proprietary implementations available - Last update Github Jan. 2025 / continuously updated</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>'- Li</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Car Simulator</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>BB-CEST</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Eclipse SDV - kanto.auto (old) will be published under a new name Eclipse OpenDUT [Carla](https://carla.org/)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Based on the W3C VISSv2 standardized interface the car simulator can act as a car and simulate VISSv2 related interfaces.   The simulator is able to create, provide and replay recorded data as well as simulate static data on the published VISSv2 based interfaces.   The solution should be able to publish data via standard transport protocols supported by the VISSv2 standard enabling get, set, sub, pub, e.g. MQTT, WS.   The car simulator offers an UI to configure data of the loaded VSS data model. Within the UI car related data can be manipulated or routes with changing data can be simulated.   The car simulator should support the whole VSS data model and data types and the interfaces should support the W3C standard of VISSv2.   The application should run locally as well as on a dedicated server based on newest web technologies</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Based on a standardized interface and data model the car simulator is able to manipulate and simulate data for services consuming data of the underlying VSS based data infrastructure.   This enables developers to simulate states without a physical car as well as quality and test engineers to verify failures and fixes based on recorded standardized data.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>CARLA</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>BB Reference implementation, extension of a Car Simulator support VSSv2 and VSS data model</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>RemotiveCloud</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>BB-CEST; BB-CSC-TC</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Diagnostics (could also be used for feeding vehicle data to emulators and other prototyping tools)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>https://cloud.remotivelabs.com/</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>RemotiveCloud - for sharing vehicle recordings, both for debugging purposes as well as for prototyping (feed data into e.g. ProtoPie and Android AAOS / AOSP emulators). The recordings can be made with the RemotiveBroker or some other logging devices following standard formats.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>RemotiveCloud enables an easy way of sharing recordings - upload to cloud and share with relevant people as suppliers and service providers to have a common place for vehicle network data (CAN etc.) for debugging and 3rd party application developers.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Nothing, create an account and get going (there is a free tier available).</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Nothing in addition to an account.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Yes, the output can be made in COVESA VSS / VISS format - both to make it easy for 3rd parties as well as to hide OEM proprietary info</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>Emil Dautovic / RemotiveLabs</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>Yes, part of Playground under the COVESA umbrella.  No active role in FEDERATE yet but there should be a good fit under WP2 projects where there is a need to collaborate in an easy way when it comes to vehicle data (from a test rig or an actual vehicle) for both debugging as well as prototyping purposes (either OEM propritary format or COVESA VSS).</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>The core RemotiveLabs components are Commercial Closed Source but reference integrations are available as source code https://github.com/remotivelabs</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>https://docs.remotivelabs.com/docs/category/remotivecloud</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Digital Twin proxy in cloud</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>BB-CMU</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Eclipse Ditto</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>The digital twin is considered as a digital representation of a vehicle (or the vehicle's configuration) as prerequisite for validation and test of SW variants prior to their deployment to a live vehicle.   Proposal for standardization are execution model with regard to simulation level (Prostep standardization &lt;https://www.prostep.org/&gt;), handling of distributed simulation, co-simulation bus and services for controller including services to extract and inject data, extract and inject algorithm dynamically (or static) during simulation, services to guarantee at least software alignment between digital and vehicle.   Defines embed service services to ensure connection with digital twin.  ***  A digital twin is a virtual representation of real-world entities and processes, synchronized at a specified frequency and fidelity.  - Digital twin systems transform business by accelerating holistic understanding, optimal decision-making, and effective action.  - Digital twins use real-time and historical data to represent the past and present and simulate predicted futures.  - Digital twins are motivated by outcomes, tailored to use cases, powered by integration, built on data, guided by domain knowledge, and implemented in IT/OT systems.  The foundational elements of the definition are captured in the first sentence: the virtual representation, the real-world entities and processes it represents, and the mechanism by which the virtual and real-world entities are synchronized.  Source: https://www.digitaltwinconsortium.org/2020/12/digital-twin-consortium-defines-digital-twin/ Digital Twin Consortium is part of the Object Management Group®.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Enables rapid prototyping, validation, and test of vehicle configurations. In scope of OTA updates, validating as many SW variants as possible (all?) to ensure the error-prone deployment of SW updates to the live fleet. Cost saving by eliminating HIL tests with a huge amount of variants.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Active diagnostics and repair services</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>App/Services store</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>App/Services store with cross-vendor-support but independent of hyper scalers</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Cloud contaier and OS</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>'- Blackberry QNX - OxidOS - Eclipse ThreadX - RedHat In-Vehicle OS (announced)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Container and OS which support executing of mixed-criticality vehicle SW</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr"/>
+      <c r="Y12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Config and settings collector</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Collects config and settings data across different SW Apps and other BBs; to transfer it to a backup location (e.g. cloud)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Data manager ensuring compliance with regulation</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>EC data act, EC AI act,… Includes authentication, access control, reporting, potentially also data sharing "for money"</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Data Spaces</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>'- Catena-X</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Data spaces supporting middleware components  and APIs</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Driver authentication</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>In-vehicle driver authentication without the need for a mobile device</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Driver Monitor</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Monitors attention and potentially medical condiion of drivers</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr"/>
+      <c r="V17" s="3" t="inlineStr"/>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="inlineStr"/>
+      <c r="Y17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>End-to-end security for C2X</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>End-to-end security for C2X consistent with global regulation</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Extended accident data recorder</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>(extending EDR = event data recorder) to better analyse accidents</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Monitoring and tracing specific HW in vehicle</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>To monitor, profile, collect HW-specific information to improve next-gen HW</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Orchestration support for energy and mobility providers</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr"/>
+      <c r="V21" s="3" t="inlineStr"/>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Secure and privacy aware voice assistant</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Secure and privacy aware voice assistant</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Vehicle data streaming</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Stream info from vehicle displays (e.g. dashboard) to mobile devices</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Vehicle monitor</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>BB-CSC</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Monitors condition of components and parts of the vehicle to support. (e.g. predictive maintenance)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>DocAsCode</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>BB-EST</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>[Open Fast Trace](https://github.com/itsallcode/openfasttrace)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>This BB aims to track and manage the software requirements of the different variants of the source code.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Several model based approaches for systems engineering and methods and tools are already established and state-of-the-art and available on the market, as well established in other industries (avionics, defense, etc.). The challenge in the automotive sector lies strongly in the variety of variants.  Driven by different product variants and the possibility of choice by the customer, this results in a high degree of combinatorics and almost exponential complexity in the subsystems.  In contrast to other industries, the automotive market with high international competition and price pressure, a wide variety of variants, functional safety and security with very long product life cycles of the vehicles in the field and the necessary software updates and hardware upgrades come together. It has become apparent that most complex, tool-based approaches to managing software requirements cannot keep pace with the capabilities of modern software development through git with the inherent capabilities of code management and automation.  If the source code of the systems is maintained in variants (branches) and developed by means of CI/CD (Continuous Integration &amp; Development) up to the control unit, the software requirements must also be manageable and versionable, just like the source code. This then allows the transfer of customized requirements from one branch to another (merge), the comparison of requirements (diff) and the automated check that all requirements along the necessary V-model artifacts (architecture, design, code, tests, test results) are covered (tracing).  To this end, we as OEMs see it as essential to use these so-called "DocAsCode" approaches more efficiently directly in the development of ECU software internally as well as along the supply chain. Of course, this does not exempt us from overall systems engineering and model-based development, in any case we consider basic research to be less relevant there.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Tom Fleischmann</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenDUT </t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>'- BB-EST, BB-CEST, BB-SC-TC, BB-CSC-TC</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>'- (Explanation: in which Functional Cluster the BB be located; if none of the existing fit new required)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>'- MWLayer</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>'- Github repo: https://github.com/eclipse-opendut/opendut</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Eclipse openDuT provides an open framework to automate the testing and validation process for automotive software and applications in a reliable, repeatable and observable way. Eclipse openDuT is hardware-agnostic with respect to the execution environment and accompanies different hardware interfaces and standards regarding the usability of the framework. Thereby, it is supporting both on-premise installations and hosting in a cloud infrastructure. Eclipse openDuT considers an eventually distributed network of real (HIL) and virtual devices (SIL) under test. Eclipse openDuT reflects hardware capabilities and constraints along with the chosen test method. Test cases are not limited to a specific domain, but it especially realizes functional and explorative security tests.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>Main Use Case are: •	(Fully automated) grey-box tests for single ECUs or clusters of ECUs •	Execution of tests over distributed test benches •	Realization of functional and explorative tests •	Coverage of Complete Security attack scenarios •	Easy interfacing and usability of the framework (Compatibility with external protocols, modularization, …) •	Observation of the test setup to verify if the test has been effective. •	Cloud/on-premises/hybrid deployments •	Adaption and full functional integration of 3rd party components (OSS, proprietary/ private source)</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>'- Reference to e.g. UN/EU CRA Cyber Resilience Act; UNECE 156 - Software update and software update management system  - Reference to defined S-BB(s)  - Reference to e.g. IS026262, AUTOSAR Spec. X</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>'- Link to required BB(s)  E.g. BB-SC StateManagement BB is a composition of other BBs</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>We expect to have a certain HW capability and or SW environment or Tool support, or a documentation, or an extra audit, or Test, or Compiler, or Prog. Language, … - Linux development environment,  - Peers &amp; Client: ARM32/64, x86_64 - Server: x86_64 - Programming language: Rust - Test environment: THEO</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>NetBird, Wireguard, TURN Sever, Keycloak, Linux-based OS, Cannelloni for CAN support, telemetry stack (Promtail, Loki, Prometheus, Tempo, Grafana), …</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>With respect to Safety, Security, Encrypted connections between clients, server and peers</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>Other clusters are needed. FC Security, FC Storage, … e.g. If FC Security : Security BBs are  needed but you can choose for example crypto BB-SC from company A or crypto BB-SC from company B; several compositions may work</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>“No”</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr">
         <is>
           <t>If Yes – e.g. The BB should be used/added in the Eclipse Blueprint A – for demo purposes, show added value,  If No – Project Proposal (e.g. WP4 in FEDERATE, or in the SDV EcoSystem Community Framework</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" s="3" t="inlineStr">
         <is>
           <t>Yes / Apache License Version 2.0</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U26" s="3" t="inlineStr">
         <is>
           <t>Yes / Apache License Version 2.0</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>AOSP Push Notification Service</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>AppLayer</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>'- &lt;https://novu.co&gt; - &lt;https://unifiedpush.org/&gt;</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>This work package aims to align on a common Android Open Source Project (AOSP) push notification service (PNS). Due to the heterogenous AOSP landscape, the solution shall be defined as a protocol that is designed in a decentralized way allowing implementing parties to choose between hosting their own PNS or using an existing one. To reduce fragmentation and to allow 3rd parties to build once and deploy anywhere, the protocol shall be guaranteed to work regardless of the underlying implementation. To help developers use the new standardized protocol, a reference implementation shall be provided.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Enable 3rd party Android apps to deliver messages, receive incoming VOIP calls or to give updates in a running app.   Lots of apps rely on being able to send messages to their clients to deliver messages or incoming VoIP calls. Because Android apps can be killed by the system at any time, they cannot rely on being able to communicate with their backend to receive these messages. To enable these use cases, a standardized PNS for AOSP (outside of Google Automotive Services GAS) is necessary and will be provided as part of this work package.    Repo: could be an enhancement of repo on &lt;https://github.com/UnifiedPush&gt;,    Technologies: Android Automotive OS, WebPuch Protocol, UnifiedPush.    Partners: COVESA members: [Automotive AOSP App Framework Standardisation Expert Group](https://wiki.covesa.global/display/WIK4/Automotive+AOSP+App+Framework+Standardization+Expert+Group), UnifiedPush</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Android Automotive OS, WebPuch Protocol, UnifiedPush</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>BB Reference implementation   New standardized protocol</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>until 30.6.2025</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" s="3" t="inlineStr">
         <is>
           <t>See Google Automotive Services FAS   &lt;https://github.com/UnifiedPush&gt;   SHIFT2SDV</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr"/>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Communication Server (S2S)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Define standard service for secured offboard communication</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>Standardized the solution</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Gateway Mirroring</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Assumption is that the "traffic shadowing/mirroring concept" from microservices defined with the Gateway being mirrored instead of specific services necessary for micro services testing. Define standard service for replay of messages and hiding of message and mirroring for test purposes</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Useful for simulation and testing. Data format maybe necessary to standardize</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Network Management</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>The network management is responsible in connected systems to orchestrate states like startup and shut down through the system. Here the services cover the overall network manager layer but also services for starting/stopping communication of nodes within the systems compare to state management.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>General policy on how to use network management with zone architecture especially for communication startup and shutdown</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR (UDPNm, CanNm, FrNm, LinNm)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>SecOS</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Define standard service for secured onboard communication</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Standardized the solution</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>[BB_Secure_Onboard_Communication](/BB-SC/MWLayer/Security/BB_Secure_Onboard_Communication.md)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Smart Charging Communication</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>&lt;https://lfenergy.org/projects/everest/&gt;</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Implementation of protocols for the smart charging of EVs</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Standard service for EV</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Standard Android VHAL</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>The standard Android VHAL implementation should be a building block enabling to seamlessly mapping of car data from underlying data middleware to Android Car API.   The solution should be able to use any data middleware using VSS and standard transport protocols enabling get, set, sub, pub, e.g. MQTT, WS. All the standard properties defined by Google shall be reused. All missing properties shall be defined using vendor properties in a standard, cross-OEM way. It should enable VSS to VHAL Property mapping using and updatable mapping file enabling:    a) definition and agreement of vendor mapping cross-OEM   b) OTA updatability   c) OEM specific mappings.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>The building block will be used using the standard Google Car API within the Android Framework</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>'- Android Automotive OS - Android VHAL - Android Car API - [COVESA Automotive AOSP App Framework Standardisation](https://covesa.global/aosp-framework/)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>BB Reference implementation / API   Standardized way (Vehicle Data mapping)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>SHIFT2SDV</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Local Update Manager</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>'- AUTOSAR: UCS - but not OSS-usable - higher-level: Eclipse Ankaios, Eclipse Kanto, Eclipse Symphony, Eclipse BlueChi</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>A Local update manager is a local instance of an (OTA) Update master. It is meant to be deployed and operated on distributed vehicle network nodes. It must provide a similar, but limited functionality compared to the OTA master. It shall be able to manage locally backup storage and rollback of software controlled by the OTA Master. The local update manager may become necessary as the OTA master will not or just with complex implementations (which may interfere with the network capabilities and the overall in-vehicle security) be able to deploy SW updates across the vehicle network within a zonal architecture. The Local update manager will deploy/install software in a dedicated local area of the vehicle network under control of the update master. It will ensure also local API for memory control and security services control.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>The local update manager may become a "must-have" within server/zone architectures to retain the capability to deploy SW updates end-to-end. Especially when there is the need to separate zones for safety/security reasons, the local update manager will be mandatory.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr"/>
+      <c r="V34" s="3" t="inlineStr"/>
+      <c r="W34" s="3" t="inlineStr"/>
+      <c r="X34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>OTA Master</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>'- AUTOSAR: UCS - but not OSS-usable - higher-level: Eclipse Ankaios, Eclipse Kanto, Eclipse Symphony, Eclipse BlueChi</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>The OTA master is a central SWC to deploy OTA SW updates within the vehicle network. Besides the basic functionality of SW installation, it implements the necessary failsafe or failover behavior to ensure the robustness of the update process (such as backup and rollover mechanism). In addition, it must manage and verify the integrity of the installed SW after it has been transferred from the backend, potentially even before installing the SW. It also coordinates local OTA salves distributed in the vehicle, by self-contained interface and command control. As a prerequisite for a successful update, the update master has also to be capable to read the vehicle configuration and control reprogramming history.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Existing, IoT based implementations of OTA Master will not carry over to zonal architectures as they - if ever - have limited ability to deploy SW across servers and zone controllers within the vehicle network. Scaling is an issue as well, as those solutions usually need continuous backend connection during the update process, thus demanding a highly scalable, costly backend infrastructure to deploy SW updates OTA for a bigger fleet. A UCM Master enables the use of standardized interfaces and Software components for OTA updates within upcoming EE architectures. A POSIX based update master can be a reasonable replacement in non-AUTOSAR environments when it implements the same basic mechanism as an UCM master.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>OTA master POSIX   OTA master ASR Adaptive (UCM Master)</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Policy Manager</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Diagnostics</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Diagnostic service applications are interpreted as the diagnostic services according to ISO 14229. Define service at vehicle level to control different access level or different permission. Each level requires previous authentication, where authentication, can remain vehicle specific.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>Establish a common concept</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>ISO 14229</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Distributed Health Management</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Platform Health Management</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>&lt;https://opentelemetry.io&gt;</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Distributed health management like state management must be orchestrated in states through the SW Partitions, subsystems, and systems as well as the reaction to "unhealthiness" of the system. Define services and hierarchy of services to handled cascading of failure detection and recovery to easily integrate safety concept.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>Services is tightly coupled to the safety concept, which is depending on the hardware capabilities and the functional safety goals. Therefore, the concrete instantiation of a distributed health management concept is highly product specific, but the infrastructure how to exchange health information and how to trigger status changes could be standardized.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR Classic   AUTOSAR Adaptive</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr"/>
+      <c r="V37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
+      <c r="Y37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Watchdog</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Platform Health Management</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Extend the traditional concept of watchdog concept (stack for external chip regular activation, deadline monitoring, alive supervision, and logical program flow supervision) to inter ECU operation in conjunction to Health Management.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>Watchdog is classically an ECU safety topic. For logical supervision and mitigation between ECUs the concept must be rethought, as AUTOSAR services enables only partial control.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR Classic</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
+      <c r="V38" s="3" t="inlineStr"/>
+      <c r="W38" s="3" t="inlineStr"/>
+      <c r="X38" s="3" t="inlineStr"/>
+      <c r="Y38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Power Management Coordination</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Power Management</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Control the handling of vehicle power in various ECU by provides generic services for handling power up and power down phases of the vehicles, to manage vehicle power transition phase and energy efficiency. It handles decision for power control based on electronic dependency and power cascading sequence. It is usually a multi-layer approach, where states are managed locally for each SW partition, for each sub system and for the complete vehicle system It is multi-layer approach    For Linux systems, systemd and how it can help with this concern is probably a highly interesting topic to investigate for this BB.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>Unified solution to facilitates integration of vehicle power management feature.</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Diagnostic Services Applications</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Runtime</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Diagnostic service applications are interpreted as the diagnostic services according to ISO 14229. Some of the service implementations are application specific like routines, data identifiers and DTCs, but at least generic hook must be defined. This includes in future also the connection to the Offboard by service orientedVehicle Diagnostic (SOVD).</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>SOVD should be standardized working with ISO 14229.</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR Classic   AUTOSAR Adaptive   ASAM SOVD</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>State Management</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Runtime</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Eclipse Piccolo</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>The State management is responsible for the start of the system "car" and the coordinated start and stop of sub systems and partitions depending on different operation modes of the vehicle. It is usually a multi-layer approach, where states are managed locally for each SW partition, for each sub system and for the complete vehicle system.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>Align vehicle operation modes that are orchestrated via proper state management. The benefit is to standardize states for applications that can then be compatible with different vehicle manufacturer.</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr"/>
+      <c r="W41" s="3" t="inlineStr"/>
+      <c r="X41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Crypto Service Manager</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Define the APIs and sequence routines for the security algorithms used by applications to access to low level hardware and/or software. Ensure that access of security routines can be run remotely.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>Standardization facilitating integration at the ECU level.</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR Classic   AUTOSAR Adaptive</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Internet Protocol Security</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Define "IPSec" a protocol used for internet key exchange, authentication header and encapsulating security payload.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>Establish a common concept.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Internet IPSec</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Intrusion Detection</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Define services to react on the events recorded by the Security event manager to security violations. IDS and IDPS (Intrusion detection and prevention system) are both considered here.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>Establish a common concept</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Secure Onboard Communication</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Define secure communication between different ECU. This includes messages signed messages with a hash (CMAC) and a counter information to be able to detect security violations (like replay attacks etc.). These services need to applied for different communication protocol common at the vehicle level to be aligned for set of secure communication routines.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>Extend the concept of AUTOSAR SecOC with a common implementation at the vehicle level.</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR SecOC</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>[BB_SecOS](/BB-SC/MWLayer/Communication/BB_SecOS.md)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
+      <c r="Y45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Security Event Manager</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>SC-BB</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Management of security related incidents (e.g. violations) and the according reaction for the overall vehicle. Define a catalogue of security events and standardize the message for security event distribution in the subsystem / system.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>ECU local and system wise concepts is necessary for propagate local security observations to vehicle wide security event manager(s).</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR Classic</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Security Transport Layer</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>## BB Tags(s)  BB-SC  ## Functional Clusters  Security  ## Layer  MWLAyer</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Define transport layer security and datagram transport layer security, as both part of the transport layer and therefore not visible on application layer (maybe except some detected security violations). Need to align all the standard. Standardization could be used on which version of TLS/dTLS to be used and reactions on security violations.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>Establish a common concept</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>Internet TLS</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Vehicle Data Collector</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>&lt;https://github.com/eclipse-sdv-blueprints/insurance&gt; &lt;https://github.com/eclipse-sdv-blueprints/fleet-management&gt;</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>A component in the vehicle which selects data of interest and uploads it to the cloud. It has access to most of the data in the car and selects by filters (AI based or rule based). Typically, the filters are modified by the cloud to enable campaigns in order to collect specific amount of data e.g. for monetization purposes. It shall support control of access services and access right</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>Standardized methods and services to access in vehicle data</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Vehicle Data Persistency</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Services for management of distributed persistent data for compatible with the different operating system (AUTOSAR Classic, Adaptive, Linux, ...) Define a high-level service capable to be mapped to the low-level API existing of OS in use in automotive. Control of robustness and refresh of standard functionality according to hardware solution. It also includes supervision of consumption and resource control (to ensure reliability of the system)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>Standardized high level service for distributing persistent data on operating system and being able to be used by advance feature (data collector, Shadowing, digital twins…)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR   Linux</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr"/>
+      <c r="V49" s="3" t="inlineStr"/>
+      <c r="W49" s="3" t="inlineStr"/>
+      <c r="X49" s="3" t="inlineStr"/>
+      <c r="Y49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Vehicle Logging and Recording</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>OpenTelemetry</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>A component in the vehicle which selects data of interest and uploads it to the cloud. It has access to most of the data in the car and selects by filters (AI based or rule based). Typically, the filters are modified by the cloud to enable campaigns in order to collect specific amount of data e.g. for monetization purposes. It shall support control of access services and access right</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>One method known is the diagnostic log and trace ("Dlt") which could be used to trace and log via any bus any information with a common time reference that is instrumented in the SW code. It may address also offboard debugging enabled by commonly used tool for dump and performance analysis. Additionally other concepts for logging that are also quite intrusive like Xcp based are established.</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR DLT   AUTOSAR XCP</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Time Service</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Define the source as a service, modulating software time based on local ECU physical Timer channel on the chip counting time even when vehicle is off.   Control the system time as time between different SW Partitions, subsystems, and systems to have a *global* valid time (selection of most accurate over several source, including diagnosis, etc..) as well as the exchange of time information between subsystems</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>Harmonization of global time interpretation by standardized protocols in the ECU architecture</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR-Classic   AUTOSAR Adaptive   Linux/Android Time</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr"/>
+      <c r="W51" s="3" t="inlineStr"/>
+      <c r="X51" s="3" t="inlineStr"/>
+      <c r="Y51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Key Management System</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Tools and Methods</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Define services for management of the keys for the ECU, subsystem, and system (secure storage, secure distribution, secure key handling). Keys have to be managed ECU local, subsystem wide and car system wide.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>To be align with various HW existing solution (HSM, TEE, etc..)</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR SecOc</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R52" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" s="3" t="inlineStr"/>
+      <c r="W52" s="3" t="inlineStr"/>
+      <c r="X52" s="3" t="inlineStr"/>
+      <c r="Y52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Key Management System</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>BB-SC</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Tools and Methods</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>MWLayer</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Define services for management of the keys for the ECU, subsystem, and system (secure storage, secure distribution, secure key handling). Keys have to be managed ECU local, subsystem wide and car system wide.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>To be align with various HW existing solution (HSM, TEE, etc..)</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>AUTOSAR SecOc</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>Conti</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" s="3" t="inlineStr"/>
+      <c r="W53" s="3" t="inlineStr"/>
+      <c r="X53" s="3" t="inlineStr"/>
+      <c r="Y53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Automotive Edge Runtime</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>BB-SC</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>OSLayer</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Eclipse Leda AutoSD (RHIVOS)</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>A runtime in the vehicle that executes workloads, typically defined by the cloud. The component can be orchestrated to manage workloads across multiple partitions or high-performance-computers. Scheduling can be static or dynamic (during runtime of the vehicle). Workloads are typically packaged as containers according to cloud native standards. There should be performance, check point analysis and means to control the container. It is recommended to applies it only for non-safety HPC partitions for non-safety functions.  interesting things to look at:  - web assembly (wasm) runtimes</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>Being able to upload container to execute function inside HPC in a standardized way (dynamic behavior and interface)</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Eclipse SDV</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R54" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr"/>
+      <c r="V54" s="3" t="inlineStr"/>
+      <c r="W54" s="3" t="inlineStr"/>
+      <c r="X54" s="3" t="inlineStr"/>
+      <c r="Y54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Shadowing</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>BB-SC-TC</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>A system working passively in the background that uses recorded data and input from sensors and cameras in the car to make its own hypothetical driving decisions. These hypothetical driving decisions are then compared to the decisions the (human) driver of the car makes. Both the recorded data and the comparison are used, amongst others, to discover unthought of edge and corner cases, and to evaluate and demonstrate the safety of autonomous functionalities. Proposal for standardization of recording services, comparison services, and process execution services are standardized in conjunction data collector and orchestrator. The rest seems to be added value of the functionality.  A digital shadow mirrors the current state and behavior of a physical entity or system.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>The use of shadowing during development (and potentially even during operation) of vehicles can enhance the ADAS algorithm/configuration development which will otherwise mostly be based on artificial test data and test drives. Shadowing will support the improvement of the vehicles in the field and enhance the safety of the users.</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr"/>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr"/>
+      <c r="W55" s="3" t="inlineStr"/>
+      <c r="X55" s="3" t="inlineStr"/>
+      <c r="Y55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Standardization of Vehicle API</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>AppLayer</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>This work package aims to create a standardized application programming interface (API) for vehicles to facilitate consistent and efficient communication between different vehicle systems and external applications.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>The existing vehicle API landscape is disparate and proprietary, leading to compatibility challenges and obstructing cross-platform app development. The work package aims to create a universal vehicle API standard to simplify third-party app integration, enhance system interoperability across manufacturers, and foster a dynamic developer ecosystem. This standardization is expected to spur innovation and the creation of advanced automotive features and services. Enabling a wide range of applications, from vehicle diagnostics to thirdparty service integration, such as insurance or smart city infrastructure.</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR Vehilce-2-X Spes</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>Reference Implementation should support REST API, …</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>Standardized Vehicle API</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="R56" s="3" t="inlineStr"/>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr"/>
+      <c r="V56" s="3" t="inlineStr"/>
+      <c r="W56" s="3" t="inlineStr"/>
+      <c r="X56" s="3" t="inlineStr"/>
+      <c r="Y56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Standardized Architectural Patterns for Cross Platform Data Service Infrastructure</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>AppLayer</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>This work package aims to develop standardized architectural patterns for a data service infrastructure that encompasses data storage, access, synchronization, and other related functionalities across different platforms.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>The lack of standardized architectural patterns for data services leads to inefficiencies, compatibility issues, and increased complexity in crossplatform data handling. This work package aims to establish a set of standardized, scalable, and adaptable architectural patterns applicable to various platforms for data services including storage, access, and synchronization. The solution enhances interoperability and efficiency of data services across platforms, reduces complexity, and simplifies integration processes.    Example usage: integration and operation of various software and hardware components within software-defined vehicles, ensuring consistent and efficient data communication across the vehicle's entire digital ecosystem.</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>Standardized architectural patterns for data service infrastructure and data management</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="R57" s="3" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr"/>
+      <c r="W57" s="3" t="inlineStr"/>
+      <c r="X57" s="3" t="inlineStr"/>
+      <c r="Y57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Standardized Description of Data from Related Domains</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>AppLayer</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>of Data from Related Domains  ## BB Tags(s)  S-BB  ## Functional Clusters   ## Layer  AppLayer  ## Known Implementation  ## ID (unique name)  ## Description  This work package focuses on developing a standardized framework for describing data from varied domains like people and the environment, ensuring uniformity, interoperability, and enhanced analytical capabilities.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>Current data description practices are inconsistent across domains such as people and the environment, leading to challenges in data integration and analysis. This work package aims to create a standardized set of data description protocols and formats applicable to these and other domains, which helps to facilitates easier data integration, enhances the accuracy of cross-domain analyses, and streamlines data management.    Example usage: Data Integration</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>Standardized data description model form related domains</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr"/>
+      <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="R58" s="3" t="inlineStr"/>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr"/>
+      <c r="V58" s="3" t="inlineStr"/>
+      <c r="W58" s="3" t="inlineStr"/>
+      <c r="X58" s="3" t="inlineStr"/>
+      <c r="Y58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Standardized Procedure and Tooling for Combining Data from Different Domains</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>AppLayer</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>This package aims to establish a standardized approach and develop tools for integrating and harmonizing data from diverse domains within the software-defined vehicle environment, ensuring effective data utilization and analysis.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>Currently, combining data from different domains is challenging due to diverse formats and standards, leading to inefficiencies and potential data loss. This work package aims to establish a unified set of procedures and tools designed for effective data integration across diverse domains to improved data integration and management, enhanced accuracy and consistency in data analysis, and streamlined workflows.  Example usage: Insight Generation Daily route, Smart Window</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr">
         <is>
           <t>Standardized tools and procedures for data integration across diverse domains</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr"/>
+      <c r="Q59" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="R59" s="3" t="inlineStr"/>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr"/>
+      <c r="V59" s="3" t="inlineStr"/>
+      <c r="W59" s="3" t="inlineStr"/>
+      <c r="X59" s="3" t="inlineStr"/>
+      <c r="Y59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Standardized Procedure and Tooling for Modelling Data from Different Domains</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>AppLayer</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Developing a standardized methodology and toolkit for data modeling in the software-defined vehicle domain, ensuring consistency, compatibility, and efficiency in data handling and analysis.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>In the context of software-defined vehicles, this work package standardizes data modeling to enhance integration and streamline development, thus supporting advanced, data-driven automotive applications.    Example usage: Employing cross-domain data modeling for automotive manufacturers, technology developers, and research institutions focused on software defined vehicles</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>Standardized Methodology/Workflow and Tooling</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr"/>
+      <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="R60" s="3" t="inlineStr"/>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr"/>
+      <c r="V60" s="3" t="inlineStr"/>
+      <c r="W60" s="3" t="inlineStr"/>
+      <c r="X60" s="3" t="inlineStr"/>
+      <c r="Y60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Legally binding formats for data exchange</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr"/>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr"/>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr"/>
+      <c r="V61" s="3" t="inlineStr"/>
+      <c r="W61" s="3" t="inlineStr"/>
+      <c r="X61" s="3" t="inlineStr"/>
+      <c r="Y61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>SOA</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Eclipse uProtocol</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Service oriented communication allows services to communicate between ECUs with each other in the vehicle typically by publish-subscribe mechanism. Typically this is enabled by middleware framework implementing a service protocol (SOME/IP, DDS,..) and providing necessary interface connectors in various programming languages.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>Standardization of SOA communication services across different vehicle manufacturer</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="R62" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr"/>
+      <c r="V62" s="3" t="inlineStr"/>
+      <c r="W62" s="3" t="inlineStr"/>
+      <c r="X62" s="3" t="inlineStr"/>
+      <c r="Y62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>sSOA</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Framework services for service-oriented architecture allowing security by design with security mechanism tight to the services (i.e. authentication of allowed service users etc.)  This needs to be tied in with the actual service mesh implementation - suggest that Eclipse uProtocol would be a good place for this topic.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>Get standardized solution whereas today each vehicle manufacturers bring its solution.</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>AUTOSAR SCREIAM</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>Conti</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R63" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" s="3" t="inlineStr"/>
+      <c r="W63" s="3" t="inlineStr"/>
+      <c r="X63" s="3" t="inlineStr"/>
+      <c r="Y63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Standardized authentication of vehicle users</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr"/>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr"/>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr"/>
+      <c r="V64" s="3" t="inlineStr"/>
+      <c r="W64" s="3" t="inlineStr"/>
+      <c r="X64" s="3" t="inlineStr"/>
+      <c r="Y64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Standardize cloud services to support international roaming of vehicles</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr"/>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr"/>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr"/>
+      <c r="V65" s="3" t="inlineStr"/>
+      <c r="W65" s="3" t="inlineStr"/>
+      <c r="X65" s="3" t="inlineStr"/>
+      <c r="Y65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Standardized Data Conversion Tools for Info-Knowledge Layers</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>s  ## BB Tags(s)  S-BB  ## Functional Clusters   ## Layer  MWLayer</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>This package aims to develop and standardize tools for converting data between the information layer (focusing on raw data collection and storage) and the knowledge layer (centered on processing data into actionable insights), ensuring accuracy and efficiency in data transformation.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>This work package addresses the inefficiencies and incompatibilities in current data conversion methods between the information and knowledge layers, which often lead to data loss or misinterpretation. The goal is to develop standardized tools for effective and accurate data conversion, streamlining processing, reducing misinterpretation risks, and enhancing overall efficiency. This will improve data analysis quality and decision making by ensuring precise transformation of raw data into actionable knowledge.    Example usage: Insight Generation</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>Standardized tools for data conversion, streamlining processing, reducing misinterpretation risks, and enhancing overall efficiency</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr"/>
+      <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="R66" s="3" t="inlineStr"/>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr"/>
+      <c r="V66" s="3" t="inlineStr"/>
+      <c r="W66" s="3" t="inlineStr"/>
+      <c r="X66" s="3" t="inlineStr"/>
+      <c r="Y66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Standardized Data Description for Vehicle Sensors, Attributes, and Actuators</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>for Vehicle Sensors, Attributes, and Actuators  ## BB Tags(s)  S-BB  ## Functional Clusters  None  ## Layer  MWLayer  ## Known Implementation  ## ID (unique name)  ## Description  Establishing a standardized framework for describing the data from vehicle sensors, attributes, and actuators within the automotive data architecture.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>Inconsistencies and lack of standardization in sensor data can lead to inefficiencies in data integration and usage across automotive systems. Developing a standardized schema for data description that can be adopted industry-wide. Streamlined integration of sensor data, improved interoperability between systems and components, reduced development costs.</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>&lt;https://www.autosar.org/fileadmin/standards/R23-11/AP/AUTOSAR_AP_SWS_SensorInterfaces.pdf&gt;</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr"/>
+      <c r="Q67" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="R67" s="3" t="inlineStr"/>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr"/>
+      <c r="V67" s="3" t="inlineStr"/>
+      <c r="W67" s="3" t="inlineStr"/>
+      <c r="X67" s="3" t="inlineStr"/>
+      <c r="Y67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Standardized data formats for digital twins</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr"/>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr"/>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr"/>
+      <c r="V68" s="3" t="inlineStr"/>
+      <c r="W68" s="3" t="inlineStr"/>
+      <c r="X68" s="3" t="inlineStr"/>
+      <c r="Y68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Stadardized HD maps formats and services</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>MWLayer</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>[HERE](https://www.here.com)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr"/>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr"/>
+      <c r="V69" s="3" t="inlineStr"/>
+      <c r="W69" s="3" t="inlineStr"/>
+      <c r="X69" s="3" t="inlineStr"/>
+      <c r="Y69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Standardized way for Reasoning on Data Streams</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>S-BB</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>This work package is dedicated to the development of a standardized framework for the analysis and reasoning of data streams within the knowledge layer of software-defined vehicles (SDVs). It aims to establish a unified approach for processing and interpreting the vast and continuous data generated by various vehicle sensors and systems. The framework is designed to enhance the efficiency and accuracy of data processing, ensuring that the knowledge layer effectively translates raw data into actionable insights. This is critical for real-time decision-making in SDVs, impacting areas such as autonomous driving, predictive maintenance, and adaptive system responses.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>Currently, the lack of a standardized method for interpreting data streams in the knowledge layer of SDVs leads to inefficiencies and potential inaccuracies in decision-making. The work package aims to create a comprehensive framework that standardizes the analysis and reasoning process of data streams in the knowledge layer of SDVs to Improve precision and speed in data interpretation, enhance real-time decision making in vehicle systems, and increase reliability and safety in vehicle performance.    Example usage: Insight Generation (Daily User Trip, Services, Entertainment)</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>Standardized framework the analysis and reasoning of data streams within the knowledge layer of software-defined vehicles (SDVs).</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr"/>
+      <c r="Q70" s="3" t="inlineStr">
         <is>
           <t>Anonymous</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr"/>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr"/>
+      <c r="V70" s="3" t="inlineStr"/>
+      <c r="W70" s="3" t="inlineStr"/>
+      <c r="X70" s="3" t="inlineStr"/>
+      <c r="Y70" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
